--- a/data/trans_orig/P5B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4268</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8293</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3987</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4115</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8791</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73502</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79678</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>70337</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67369</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>147977</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>143799</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>150622</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>94,55%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70337</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67650</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>147977</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>143301</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>150272</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,22%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63176</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68056</t>
+          <t>68061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>61633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127066</t>
+          <t>127667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134240</t>
+          <t>134298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81506</t>
+          <t>81313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139162</t>
+          <t>139201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137892</t>
+          <t>137568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147166</t>
+          <t>146922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140640</t>
+          <t>140620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147214</t>
+          <t>147233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281448</t>
+          <t>281337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292458</t>
+          <t>292730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>13824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60622</t>
+          <t>60333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67636</t>
+          <t>67066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76730</t>
+          <t>76543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82744</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140003</t>
+          <t>139828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149161</t>
+          <t>149160</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +2498,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>5967</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>11100</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>5967</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>2938</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11039</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74210</t>
+          <t>74208</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71045</t>
+          <t>71077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +2611,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>141295</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>136162</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>144528</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>98,14%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>141295</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>136223</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>144324</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>45436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475053</t>
+          <t>474695</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>489512</t>
+          <t>489592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>505845</t>
+          <t>504686</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>518437</t>
+          <t>517976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>985327</t>
+          <t>985789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1004593</t>
+          <t>1004852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>54559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>60002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68661</t>
+          <t>67720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124549</t>
+          <t>125940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131607</t>
+          <t>132028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60479</t>
+          <t>60548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>63290</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126352</t>
+          <t>126464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132394</t>
+          <t>132402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62446</t>
+          <t>62017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>64524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130133</t>
+          <t>129413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131138</t>
+          <t>131334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135984</t>
+          <t>135976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153972</t>
+          <t>154045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160685</t>
+          <t>160684</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288811</t>
+          <t>288293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295962</t>
+          <t>295785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89557</t>
+          <t>89974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181956</t>
+          <t>181512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48178</t>
+          <t>48304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68032</t>
+          <t>67754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73380</t>
+          <t>73376</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118383</t>
+          <t>118552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125273</t>
+          <t>125262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26308</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>460636</t>
+          <t>459603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>470370</t>
+          <t>470548</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>521238</t>
+          <t>521481</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>531539</t>
+          <t>531721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>985262</t>
+          <t>985717</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>999276</t>
+          <t>999779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79218</t>
+          <t>78678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89677</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170476</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156291</t>
+          <t>156084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162493</t>
+          <t>162452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161482</t>
+          <t>162403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169165</t>
+          <t>169057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321710</t>
+          <t>321557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330661</t>
+          <t>330627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94533</t>
+          <t>94519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100322</t>
+          <t>100331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94754</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191702</t>
+          <t>190797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198775</t>
+          <t>198717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55432</t>
+          <t>55472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59778</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123286</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>506172</t>
+          <t>506803</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>516037</t>
+          <t>516261</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>558668</t>
+          <t>558408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>566604</t>
+          <t>566508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1068323</t>
+          <t>1068750</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1081177</t>
+          <t>1081019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129753</t>
+          <t>129619</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234092</t>
+          <t>233712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91255</t>
+          <t>91264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88500</t>
+          <t>88177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94989</t>
+          <t>94979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182013</t>
+          <t>182642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189346</t>
+          <t>189336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58346</t>
+          <t>58935</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110762</t>
+          <t>110570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85836</t>
+          <t>92080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122745</t>
+          <t>112297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132989</t>
+          <t>126745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212312</t>
+          <t>212808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314352</t>
+          <t>324800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>435585</t>
+          <t>435600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112632</t>
+          <t>112660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118782</t>
+          <t>118785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157208</t>
+          <t>156923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272696</t>
+          <t>272880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280226</t>
+          <t>280512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68097</t>
+          <t>68626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>137557</t>
+          <t>137121</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135814</t>
+          <t>120684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145152</t>
+          <t>171521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>521582</t>
+          <t>536712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654245</t>
+          <t>654670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>730891</t>
+          <t>730500</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>741939</t>
+          <t>742412</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1259828</t>
+          <t>1233459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1393513</t>
+          <t>1393171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
